--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1024,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122208969</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102153</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>267005</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ugglarpsbjörnbär</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rubus cordatiformis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Neuman) Ryde</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ugglarp, Vassviksvägen, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>354693</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6299182</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Eftra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>70X30 m</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulf Ryde</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulf Ryde</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>122208969</v>
       </c>
       <c r="B5" t="n">
-        <v>102179</v>
+        <v>102189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>122208969</v>
       </c>
       <c r="B5" t="n">
-        <v>102189</v>
+        <v>102202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>122208969</v>
       </c>
       <c r="B5" t="n">
-        <v>102202</v>
+        <v>102207</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>122208969</v>
       </c>
       <c r="B5" t="n">
-        <v>102207</v>
+        <v>102216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,11 +1043,6 @@
       </c>
       <c r="E5" t="n">
         <v>267005</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ugglarpsbjörnbär</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>122208969</v>
       </c>
       <c r="B5" t="n">
-        <v>102216</v>
+        <v>102229</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,6 +1043,11 @@
       </c>
       <c r="E5" t="n">
         <v>267005</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ugglarpsbjörnbär</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 61238-2019 artfynd.xlsx
+++ b/artfynd/A 61238-2019 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>122208969</v>
       </c>
       <c r="B5" t="n">
-        <v>102229</v>
+        <v>102242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
